--- a/GameData/DataTables/Board/ObstacleTable.xlsx
+++ b/GameData/DataTables/Board/ObstacleTable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,6 +463,11 @@
           <t>PassDirection</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ExtraData</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -495,6 +500,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -525,6 +535,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>方向参数，无方向为 -1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>逐项参数，k=v;k=v 分号分隔；空表示用代码默认值</t>
         </is>
       </c>
     </row>
@@ -565,6 +580,11 @@
       <c r="G6" t="n">
         <v>-1</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RootBlastOncePerRoot=1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -584,6 +604,11 @@
       <c r="G7" t="n">
         <v>-1</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>InitialOpen=0;ToggleOncePerRoot=1;DeferCloseWhenOccupied=1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -622,6 +647,11 @@
       <c r="G9" t="n">
         <v>-1</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AllowTags=normal;InitialClampedEntityId=0;ReleaseWindowTaps=1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -641,6 +671,11 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ToggleDirection=3</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -660,6 +695,11 @@
       <c r="G11" t="n">
         <v>-1</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>GrowthPerTap=1;SegmentMaxDurability=1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -678,6 +718,11 @@
       </c>
       <c r="G12" t="n">
         <v>-1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AttachedPartitions=2;ProtectedObject=0;Repairable=1</t>
+        </is>
       </c>
     </row>
   </sheetData>
